--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1121,6 +1121,2136 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127862450</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>405624</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6771580</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127862464</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91352</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>405525</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6771517</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127862496</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80083</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>405678</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6771470</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127862510</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>405561</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6771580</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127862482</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91338</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>405519</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6771445</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127862452</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>405624</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6771580</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127862468</v>
+      </c>
+      <c r="B12" t="n">
+        <v>88741</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>510</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>405599</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6771493</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127862454</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92035</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>405619</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6771567</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127862498</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>405494</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6771573</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127862508</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91352</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>405561</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6771580</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127862480</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91303</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>405519</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6771445</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127862490</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80152</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>405479</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6771576</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127862470</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80123</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>405608</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6771494</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127862488</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>405486</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6771515</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127862474</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98376</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>405573</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6771501</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127862466</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>405526</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6771489</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127862506</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>405534</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6771422</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127862448</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80123</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>405677</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6771484</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127862494</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91303</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>405529</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6771570</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127862492</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>405529</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6771570</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127862484</v>
+      </c>
+      <c r="B26" t="n">
+        <v>88741</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>510</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>405475</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6771490</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127862442</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fjällsåskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>405496</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6771473</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>127862450</v>
       </c>
       <c r="B6" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>127862464</v>
       </c>
       <c r="B7" t="n">
-        <v>91352</v>
+        <v>91355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127862496</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>80086</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>127862510</v>
       </c>
       <c r="B9" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>127862482</v>
       </c>
       <c r="B10" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>127862452</v>
       </c>
       <c r="B11" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>127862468</v>
       </c>
       <c r="B12" t="n">
-        <v>88741</v>
+        <v>88744</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>127862454</v>
       </c>
       <c r="B13" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>127862498</v>
       </c>
       <c r="B14" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>127862508</v>
       </c>
       <c r="B15" t="n">
-        <v>91352</v>
+        <v>91355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>127862480</v>
       </c>
       <c r="B16" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127862490</v>
       </c>
       <c r="B17" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>127862470</v>
       </c>
       <c r="B18" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>127862488</v>
       </c>
       <c r="B19" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>127862474</v>
       </c>
       <c r="B20" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>127862466</v>
       </c>
       <c r="B21" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>127862506</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>127862448</v>
       </c>
       <c r="B23" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>127862494</v>
       </c>
       <c r="B24" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>127862484</v>
       </c>
       <c r="B26" t="n">
-        <v>88741</v>
+        <v>88744</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>127862442</v>
       </c>
       <c r="B27" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>127862450</v>
       </c>
       <c r="B6" t="n">
-        <v>92038</v>
+        <v>92046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>127862464</v>
       </c>
       <c r="B7" t="n">
-        <v>91355</v>
+        <v>91363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127862496</v>
       </c>
       <c r="B8" t="n">
-        <v>80086</v>
+        <v>80092</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>127862510</v>
       </c>
       <c r="B9" t="n">
-        <v>92038</v>
+        <v>92046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>127862482</v>
       </c>
       <c r="B10" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>127862452</v>
       </c>
       <c r="B11" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>127862468</v>
       </c>
       <c r="B12" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>127862454</v>
       </c>
       <c r="B13" t="n">
-        <v>92038</v>
+        <v>92046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>127862498</v>
       </c>
       <c r="B14" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>127862508</v>
       </c>
       <c r="B15" t="n">
-        <v>91355</v>
+        <v>91363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>127862480</v>
       </c>
       <c r="B16" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2190,32 +2190,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127862490</v>
+        <v>127862488</v>
       </c>
       <c r="B17" t="n">
-        <v>80155</v>
+        <v>91367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405479</v>
+        <v>405486</v>
       </c>
       <c r="R17" t="n">
-        <v>6771576</v>
+        <v>6771515</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2287,32 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127862470</v>
+        <v>127862490</v>
       </c>
       <c r="B18" t="n">
-        <v>80126</v>
+        <v>80161</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405608</v>
+        <v>405479</v>
       </c>
       <c r="R18" t="n">
-        <v>6771494</v>
+        <v>6771576</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127862488</v>
+        <v>127862470</v>
       </c>
       <c r="B19" t="n">
-        <v>91359</v>
+        <v>80132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405486</v>
+        <v>405608</v>
       </c>
       <c r="R19" t="n">
-        <v>6771515</v>
+        <v>6771494</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2484,7 +2484,7 @@
         <v>127862474</v>
       </c>
       <c r="B20" t="n">
-        <v>98379</v>
+        <v>98387</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>127862466</v>
       </c>
       <c r="B21" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>127862506</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>127862448</v>
       </c>
       <c r="B23" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>127862494</v>
       </c>
       <c r="B24" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>127862484</v>
       </c>
       <c r="B26" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>127862442</v>
       </c>
       <c r="B27" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>127862450</v>
       </c>
       <c r="B6" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>127862464</v>
       </c>
       <c r="B7" t="n">
-        <v>91363</v>
+        <v>91364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>127862510</v>
       </c>
       <c r="B9" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>127862482</v>
       </c>
       <c r="B10" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>127862452</v>
       </c>
       <c r="B11" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>127862468</v>
       </c>
       <c r="B12" t="n">
-        <v>88752</v>
+        <v>88753</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127862454</v>
+        <v>127862508</v>
       </c>
       <c r="B13" t="n">
-        <v>92046</v>
+        <v>91364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405619</v>
+        <v>405561</v>
       </c>
       <c r="R13" t="n">
-        <v>6771567</v>
+        <v>6771580</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127862498</v>
+        <v>127862454</v>
       </c>
       <c r="B14" t="n">
-        <v>91367</v>
+        <v>92047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405494</v>
+        <v>405619</v>
       </c>
       <c r="R14" t="n">
-        <v>6771573</v>
+        <v>6771567</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127862508</v>
+        <v>127862498</v>
       </c>
       <c r="B15" t="n">
-        <v>91363</v>
+        <v>91368</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405561</v>
+        <v>405494</v>
       </c>
       <c r="R15" t="n">
-        <v>6771580</v>
+        <v>6771573</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2096,7 +2096,7 @@
         <v>127862480</v>
       </c>
       <c r="B16" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2190,32 +2190,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127862488</v>
+        <v>127862490</v>
       </c>
       <c r="B17" t="n">
-        <v>91367</v>
+        <v>80161</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405486</v>
+        <v>405479</v>
       </c>
       <c r="R17" t="n">
-        <v>6771515</v>
+        <v>6771576</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2287,32 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127862490</v>
+        <v>127862470</v>
       </c>
       <c r="B18" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405479</v>
+        <v>405608</v>
       </c>
       <c r="R18" t="n">
-        <v>6771576</v>
+        <v>6771494</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127862470</v>
+        <v>127862488</v>
       </c>
       <c r="B19" t="n">
-        <v>80132</v>
+        <v>91368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405608</v>
+        <v>405486</v>
       </c>
       <c r="R19" t="n">
-        <v>6771494</v>
+        <v>6771515</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2484,7 +2484,7 @@
         <v>127862474</v>
       </c>
       <c r="B20" t="n">
-        <v>98387</v>
+        <v>98388</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>127862466</v>
       </c>
       <c r="B21" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>127862494</v>
       </c>
       <c r="B24" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>127862484</v>
       </c>
       <c r="B26" t="n">
-        <v>88752</v>
+        <v>88753</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>127862442</v>
       </c>
       <c r="B27" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127862450</v>
+        <v>127862496</v>
       </c>
       <c r="B6" t="n">
-        <v>92047</v>
+        <v>80092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405624</v>
+        <v>405678</v>
       </c>
       <c r="R6" t="n">
-        <v>6771580</v>
+        <v>6771470</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127862464</v>
+        <v>127862450</v>
       </c>
       <c r="B7" t="n">
-        <v>91364</v>
+        <v>92047</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405525</v>
+        <v>405624</v>
       </c>
       <c r="R7" t="n">
-        <v>6771517</v>
+        <v>6771580</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127862496</v>
+        <v>127862464</v>
       </c>
       <c r="B8" t="n">
-        <v>80092</v>
+        <v>91364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405678</v>
+        <v>405525</v>
       </c>
       <c r="R8" t="n">
-        <v>6771470</v>
+        <v>6771517</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1802,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127862508</v>
+        <v>127862454</v>
       </c>
       <c r="B13" t="n">
-        <v>91364</v>
+        <v>92047</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405561</v>
+        <v>405619</v>
       </c>
       <c r="R13" t="n">
-        <v>6771580</v>
+        <v>6771567</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127862454</v>
+        <v>127862498</v>
       </c>
       <c r="B14" t="n">
-        <v>92047</v>
+        <v>91368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405619</v>
+        <v>405494</v>
       </c>
       <c r="R14" t="n">
-        <v>6771567</v>
+        <v>6771573</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127862498</v>
+        <v>127862508</v>
       </c>
       <c r="B15" t="n">
-        <v>91368</v>
+        <v>91364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405494</v>
+        <v>405561</v>
       </c>
       <c r="R15" t="n">
-        <v>6771573</v>
+        <v>6771580</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -1123,32 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127862496</v>
+        <v>127862464</v>
       </c>
       <c r="B6" t="n">
-        <v>80092</v>
+        <v>91365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405678</v>
+        <v>405525</v>
       </c>
       <c r="R6" t="n">
-        <v>6771470</v>
+        <v>6771517</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127862450</v>
+        <v>127862496</v>
       </c>
       <c r="B7" t="n">
-        <v>92047</v>
+        <v>80092</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405624</v>
+        <v>405678</v>
       </c>
       <c r="R7" t="n">
-        <v>6771580</v>
+        <v>6771470</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127862464</v>
+        <v>127862450</v>
       </c>
       <c r="B8" t="n">
-        <v>91364</v>
+        <v>92048</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405525</v>
+        <v>405624</v>
       </c>
       <c r="R8" t="n">
-        <v>6771517</v>
+        <v>6771580</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,7 +1417,7 @@
         <v>127862510</v>
       </c>
       <c r="B9" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>127862482</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127862452</v>
+        <v>127862468</v>
       </c>
       <c r="B11" t="n">
-        <v>91368</v>
+        <v>88754</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405624</v>
+        <v>405599</v>
       </c>
       <c r="R11" t="n">
-        <v>6771580</v>
+        <v>6771493</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127862468</v>
+        <v>127862452</v>
       </c>
       <c r="B12" t="n">
-        <v>88753</v>
+        <v>91369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405599</v>
+        <v>405624</v>
       </c>
       <c r="R12" t="n">
-        <v>6771493</v>
+        <v>6771580</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1802,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127862454</v>
+        <v>127862508</v>
       </c>
       <c r="B13" t="n">
-        <v>92047</v>
+        <v>91365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405619</v>
+        <v>405561</v>
       </c>
       <c r="R13" t="n">
-        <v>6771567</v>
+        <v>6771580</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127862498</v>
+        <v>127862454</v>
       </c>
       <c r="B14" t="n">
-        <v>91368</v>
+        <v>92048</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405494</v>
+        <v>405619</v>
       </c>
       <c r="R14" t="n">
-        <v>6771573</v>
+        <v>6771567</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127862508</v>
+        <v>127862498</v>
       </c>
       <c r="B15" t="n">
-        <v>91364</v>
+        <v>91369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405561</v>
+        <v>405494</v>
       </c>
       <c r="R15" t="n">
-        <v>6771580</v>
+        <v>6771573</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2096,7 +2096,7 @@
         <v>127862480</v>
       </c>
       <c r="B16" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>127862488</v>
       </c>
       <c r="B19" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>127862474</v>
       </c>
       <c r="B20" t="n">
-        <v>98388</v>
+        <v>98389</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>127862466</v>
       </c>
       <c r="B21" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>127862494</v>
       </c>
       <c r="B24" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>127862484</v>
       </c>
       <c r="B26" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>127862442</v>
       </c>
       <c r="B27" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>127862464</v>
       </c>
       <c r="B6" t="n">
-        <v>91365</v>
+        <v>91366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127862496</v>
+        <v>127862450</v>
       </c>
       <c r="B7" t="n">
-        <v>80092</v>
+        <v>92049</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405678</v>
+        <v>405624</v>
       </c>
       <c r="R7" t="n">
-        <v>6771470</v>
+        <v>6771580</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127862450</v>
+        <v>127862496</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>80092</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405624</v>
+        <v>405678</v>
       </c>
       <c r="R8" t="n">
-        <v>6771580</v>
+        <v>6771470</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,7 +1417,7 @@
         <v>127862510</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>127862482</v>
       </c>
       <c r="B10" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>127862468</v>
       </c>
       <c r="B11" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>127862452</v>
       </c>
       <c r="B12" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>127862508</v>
       </c>
       <c r="B13" t="n">
-        <v>91365</v>
+        <v>91366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>127862454</v>
       </c>
       <c r="B14" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>127862498</v>
       </c>
       <c r="B15" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>127862480</v>
       </c>
       <c r="B16" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>127862488</v>
       </c>
       <c r="B19" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>127862474</v>
       </c>
       <c r="B20" t="n">
-        <v>98389</v>
+        <v>98390</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>127862466</v>
       </c>
       <c r="B21" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>127862494</v>
       </c>
       <c r="B24" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>127862484</v>
       </c>
       <c r="B26" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>127862442</v>
       </c>
       <c r="B27" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -1123,32 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127862464</v>
+        <v>127862450</v>
       </c>
       <c r="B6" t="n">
-        <v>91366</v>
+        <v>92049</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405525</v>
+        <v>405624</v>
       </c>
       <c r="R6" t="n">
-        <v>6771517</v>
+        <v>6771580</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127862450</v>
+        <v>127862464</v>
       </c>
       <c r="B7" t="n">
-        <v>92049</v>
+        <v>91366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405624</v>
+        <v>405525</v>
       </c>
       <c r="R7" t="n">
-        <v>6771580</v>
+        <v>6771517</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1802,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127862508</v>
+        <v>127862454</v>
       </c>
       <c r="B13" t="n">
-        <v>91366</v>
+        <v>92049</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405561</v>
+        <v>405619</v>
       </c>
       <c r="R13" t="n">
-        <v>6771580</v>
+        <v>6771567</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127862454</v>
+        <v>127862508</v>
       </c>
       <c r="B14" t="n">
-        <v>92049</v>
+        <v>91366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405619</v>
+        <v>405561</v>
       </c>
       <c r="R14" t="n">
-        <v>6771567</v>
+        <v>6771580</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127862506</v>
+        <v>127862448</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>405534</v>
+        <v>405677</v>
       </c>
       <c r="R22" t="n">
-        <v>6771422</v>
+        <v>6771484</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127862448</v>
+        <v>127862506</v>
       </c>
       <c r="B23" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>405677</v>
+        <v>405534</v>
       </c>
       <c r="R23" t="n">
-        <v>6771484</v>
+        <v>6771422</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -2190,32 +2190,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127862490</v>
+        <v>127862488</v>
       </c>
       <c r="B17" t="n">
-        <v>80161</v>
+        <v>91370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405479</v>
+        <v>405486</v>
       </c>
       <c r="R17" t="n">
-        <v>6771576</v>
+        <v>6771515</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2287,32 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127862470</v>
+        <v>127862490</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405608</v>
+        <v>405479</v>
       </c>
       <c r="R18" t="n">
-        <v>6771494</v>
+        <v>6771576</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127862488</v>
+        <v>127862470</v>
       </c>
       <c r="B19" t="n">
-        <v>91370</v>
+        <v>80132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405486</v>
+        <v>405608</v>
       </c>
       <c r="R19" t="n">
-        <v>6771515</v>
+        <v>6771494</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -2190,32 +2190,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127862488</v>
+        <v>127862490</v>
       </c>
       <c r="B17" t="n">
-        <v>91370</v>
+        <v>80161</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405486</v>
+        <v>405479</v>
       </c>
       <c r="R17" t="n">
-        <v>6771515</v>
+        <v>6771576</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2287,32 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127862490</v>
+        <v>127862470</v>
       </c>
       <c r="B18" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405479</v>
+        <v>405608</v>
       </c>
       <c r="R18" t="n">
-        <v>6771576</v>
+        <v>6771494</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127862470</v>
+        <v>127862488</v>
       </c>
       <c r="B19" t="n">
-        <v>80132</v>
+        <v>91370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405608</v>
+        <v>405486</v>
       </c>
       <c r="R19" t="n">
-        <v>6771494</v>
+        <v>6771515</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>127862450</v>
       </c>
       <c r="B6" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>127862464</v>
       </c>
       <c r="B7" t="n">
-        <v>91366</v>
+        <v>91374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127862496</v>
       </c>
       <c r="B8" t="n">
-        <v>80092</v>
+        <v>80095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>127862510</v>
       </c>
       <c r="B9" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>127862482</v>
       </c>
       <c r="B10" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>127862468</v>
       </c>
       <c r="B11" t="n">
-        <v>88755</v>
+        <v>88761</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>127862452</v>
       </c>
       <c r="B12" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>127862454</v>
       </c>
       <c r="B13" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127862508</v>
+        <v>127862498</v>
       </c>
       <c r="B14" t="n">
-        <v>91366</v>
+        <v>91378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405561</v>
+        <v>405494</v>
       </c>
       <c r="R14" t="n">
-        <v>6771580</v>
+        <v>6771573</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127862498</v>
+        <v>127862508</v>
       </c>
       <c r="B15" t="n">
-        <v>91370</v>
+        <v>91374</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405494</v>
+        <v>405561</v>
       </c>
       <c r="R15" t="n">
-        <v>6771573</v>
+        <v>6771580</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2096,7 +2096,7 @@
         <v>127862480</v>
       </c>
       <c r="B16" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127862490</v>
       </c>
       <c r="B17" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>127862470</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>127862488</v>
       </c>
       <c r="B19" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>127862474</v>
       </c>
       <c r="B20" t="n">
-        <v>98390</v>
+        <v>98398</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>127862466</v>
       </c>
       <c r="B21" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127862448</v>
+        <v>127862506</v>
       </c>
       <c r="B22" t="n">
-        <v>80132</v>
+        <v>79032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>405677</v>
+        <v>405534</v>
       </c>
       <c r="R22" t="n">
-        <v>6771484</v>
+        <v>6771422</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127862506</v>
+        <v>127862448</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>80135</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>405534</v>
+        <v>405677</v>
       </c>
       <c r="R23" t="n">
-        <v>6771422</v>
+        <v>6771484</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2868,7 +2868,7 @@
         <v>127862494</v>
       </c>
       <c r="B24" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>127862484</v>
       </c>
       <c r="B26" t="n">
-        <v>88755</v>
+        <v>88761</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>127862442</v>
       </c>
       <c r="B27" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127862450</v>
+        <v>127862496</v>
       </c>
       <c r="B6" t="n">
-        <v>92057</v>
+        <v>80148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405624</v>
+        <v>405678</v>
       </c>
       <c r="R6" t="n">
-        <v>6771580</v>
+        <v>6771470</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127862464</v>
+        <v>127862450</v>
       </c>
       <c r="B7" t="n">
-        <v>91374</v>
+        <v>92149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405525</v>
+        <v>405624</v>
       </c>
       <c r="R7" t="n">
-        <v>6771517</v>
+        <v>6771580</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127862496</v>
+        <v>127862464</v>
       </c>
       <c r="B8" t="n">
-        <v>80095</v>
+        <v>91466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405678</v>
+        <v>405525</v>
       </c>
       <c r="R8" t="n">
-        <v>6771470</v>
+        <v>6771517</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,7 +1417,7 @@
         <v>127862510</v>
       </c>
       <c r="B9" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>127862482</v>
       </c>
       <c r="B10" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>127862468</v>
       </c>
       <c r="B11" t="n">
-        <v>88761</v>
+        <v>88853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>127862452</v>
       </c>
       <c r="B12" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>127862454</v>
       </c>
       <c r="B13" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127862498</v>
+        <v>127862508</v>
       </c>
       <c r="B14" t="n">
-        <v>91378</v>
+        <v>91466</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405494</v>
+        <v>405561</v>
       </c>
       <c r="R14" t="n">
-        <v>6771573</v>
+        <v>6771580</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127862508</v>
+        <v>127862498</v>
       </c>
       <c r="B15" t="n">
-        <v>91374</v>
+        <v>91470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405561</v>
+        <v>405494</v>
       </c>
       <c r="R15" t="n">
-        <v>6771580</v>
+        <v>6771573</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2096,7 +2096,7 @@
         <v>127862480</v>
       </c>
       <c r="B16" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127862490</v>
       </c>
       <c r="B17" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127862470</v>
+        <v>127862488</v>
       </c>
       <c r="B18" t="n">
-        <v>80135</v>
+        <v>91470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405608</v>
+        <v>405486</v>
       </c>
       <c r="R18" t="n">
-        <v>6771494</v>
+        <v>6771515</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127862488</v>
+        <v>127862470</v>
       </c>
       <c r="B19" t="n">
-        <v>91378</v>
+        <v>80188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405486</v>
+        <v>405608</v>
       </c>
       <c r="R19" t="n">
-        <v>6771515</v>
+        <v>6771494</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2484,7 +2484,7 @@
         <v>127862474</v>
       </c>
       <c r="B20" t="n">
-        <v>98398</v>
+        <v>98491</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>127862466</v>
       </c>
       <c r="B21" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127862506</v>
+        <v>127862448</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>80188</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>405534</v>
+        <v>405677</v>
       </c>
       <c r="R22" t="n">
-        <v>6771422</v>
+        <v>6771484</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127862448</v>
+        <v>127862506</v>
       </c>
       <c r="B23" t="n">
-        <v>80135</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>405677</v>
+        <v>405534</v>
       </c>
       <c r="R23" t="n">
-        <v>6771484</v>
+        <v>6771422</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2868,7 +2868,7 @@
         <v>127862494</v>
       </c>
       <c r="B24" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>127862484</v>
       </c>
       <c r="B26" t="n">
-        <v>88761</v>
+        <v>88853</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>127862442</v>
       </c>
       <c r="B27" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127862496</v>
+        <v>127862450</v>
       </c>
       <c r="B6" t="n">
-        <v>80148</v>
+        <v>92149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405678</v>
+        <v>405624</v>
       </c>
       <c r="R6" t="n">
-        <v>6771470</v>
+        <v>6771580</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127862450</v>
+        <v>127862464</v>
       </c>
       <c r="B7" t="n">
-        <v>92149</v>
+        <v>91466</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405624</v>
+        <v>405525</v>
       </c>
       <c r="R7" t="n">
-        <v>6771580</v>
+        <v>6771517</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127862464</v>
+        <v>127862496</v>
       </c>
       <c r="B8" t="n">
-        <v>91466</v>
+        <v>80148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405525</v>
+        <v>405678</v>
       </c>
       <c r="R8" t="n">
-        <v>6771517</v>
+        <v>6771470</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127862468</v>
+        <v>127862452</v>
       </c>
       <c r="B11" t="n">
-        <v>88853</v>
+        <v>91470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405599</v>
+        <v>405624</v>
       </c>
       <c r="R11" t="n">
-        <v>6771493</v>
+        <v>6771580</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127862452</v>
+        <v>127862468</v>
       </c>
       <c r="B12" t="n">
-        <v>91470</v>
+        <v>88853</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405624</v>
+        <v>405599</v>
       </c>
       <c r="R12" t="n">
-        <v>6771580</v>
+        <v>6771493</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1802,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127862454</v>
+        <v>127862498</v>
       </c>
       <c r="B13" t="n">
-        <v>92149</v>
+        <v>91470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405619</v>
+        <v>405494</v>
       </c>
       <c r="R13" t="n">
-        <v>6771567</v>
+        <v>6771573</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127862508</v>
+        <v>127862454</v>
       </c>
       <c r="B14" t="n">
-        <v>91466</v>
+        <v>92149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405561</v>
+        <v>405619</v>
       </c>
       <c r="R14" t="n">
-        <v>6771580</v>
+        <v>6771567</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127862498</v>
+        <v>127862508</v>
       </c>
       <c r="B15" t="n">
-        <v>91470</v>
+        <v>91466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405494</v>
+        <v>405561</v>
       </c>
       <c r="R15" t="n">
-        <v>6771573</v>
+        <v>6771580</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127862488</v>
+        <v>127862470</v>
       </c>
       <c r="B18" t="n">
-        <v>91470</v>
+        <v>80188</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405486</v>
+        <v>405608</v>
       </c>
       <c r="R18" t="n">
-        <v>6771515</v>
+        <v>6771494</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127862470</v>
+        <v>127862488</v>
       </c>
       <c r="B19" t="n">
-        <v>80188</v>
+        <v>91470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405608</v>
+        <v>405486</v>
       </c>
       <c r="R19" t="n">
-        <v>6771494</v>
+        <v>6771515</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127862448</v>
+        <v>127862506</v>
       </c>
       <c r="B22" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>405677</v>
+        <v>405534</v>
       </c>
       <c r="R22" t="n">
-        <v>6771484</v>
+        <v>6771422</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127862506</v>
+        <v>127862448</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>405534</v>
+        <v>405677</v>
       </c>
       <c r="R23" t="n">
-        <v>6771422</v>
+        <v>6771484</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127862452</v>
+        <v>127862468</v>
       </c>
       <c r="B11" t="n">
-        <v>91470</v>
+        <v>88853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405624</v>
+        <v>405599</v>
       </c>
       <c r="R11" t="n">
-        <v>6771580</v>
+        <v>6771493</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127862468</v>
+        <v>127862452</v>
       </c>
       <c r="B12" t="n">
-        <v>88853</v>
+        <v>91470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405599</v>
+        <v>405624</v>
       </c>
       <c r="R12" t="n">
-        <v>6771493</v>
+        <v>6771580</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1802,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127862498</v>
+        <v>127862454</v>
       </c>
       <c r="B13" t="n">
-        <v>91470</v>
+        <v>92149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405494</v>
+        <v>405619</v>
       </c>
       <c r="R13" t="n">
-        <v>6771573</v>
+        <v>6771567</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127862454</v>
+        <v>127862498</v>
       </c>
       <c r="B14" t="n">
-        <v>92149</v>
+        <v>91470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405619</v>
+        <v>405494</v>
       </c>
       <c r="R14" t="n">
-        <v>6771567</v>
+        <v>6771573</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -1802,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127862454</v>
+        <v>127862508</v>
       </c>
       <c r="B13" t="n">
-        <v>92149</v>
+        <v>91466</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405619</v>
+        <v>405561</v>
       </c>
       <c r="R13" t="n">
-        <v>6771567</v>
+        <v>6771580</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127862498</v>
+        <v>127862454</v>
       </c>
       <c r="B14" t="n">
-        <v>91470</v>
+        <v>92149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405494</v>
+        <v>405619</v>
       </c>
       <c r="R14" t="n">
-        <v>6771573</v>
+        <v>6771567</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127862508</v>
+        <v>127862498</v>
       </c>
       <c r="B15" t="n">
-        <v>91466</v>
+        <v>91470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405561</v>
+        <v>405494</v>
       </c>
       <c r="R15" t="n">
-        <v>6771580</v>
+        <v>6771573</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>127862450</v>
       </c>
       <c r="B6" t="n">
-        <v>92149</v>
+        <v>92161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>127862464</v>
       </c>
       <c r="B7" t="n">
-        <v>91466</v>
+        <v>91478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127862496</v>
       </c>
       <c r="B8" t="n">
-        <v>80148</v>
+        <v>80152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>127862510</v>
       </c>
       <c r="B9" t="n">
-        <v>92149</v>
+        <v>92161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>127862482</v>
       </c>
       <c r="B10" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127862468</v>
+        <v>127862452</v>
       </c>
       <c r="B11" t="n">
-        <v>88853</v>
+        <v>91482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405599</v>
+        <v>405624</v>
       </c>
       <c r="R11" t="n">
-        <v>6771493</v>
+        <v>6771580</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127862452</v>
+        <v>127862468</v>
       </c>
       <c r="B12" t="n">
-        <v>91470</v>
+        <v>88865</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405624</v>
+        <v>405599</v>
       </c>
       <c r="R12" t="n">
-        <v>6771580</v>
+        <v>6771493</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1802,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127862508</v>
+        <v>127862454</v>
       </c>
       <c r="B13" t="n">
-        <v>91466</v>
+        <v>92161</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405561</v>
+        <v>405619</v>
       </c>
       <c r="R13" t="n">
-        <v>6771580</v>
+        <v>6771567</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127862454</v>
+        <v>127862498</v>
       </c>
       <c r="B14" t="n">
-        <v>92149</v>
+        <v>91482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405619</v>
+        <v>405494</v>
       </c>
       <c r="R14" t="n">
-        <v>6771567</v>
+        <v>6771573</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127862498</v>
+        <v>127862508</v>
       </c>
       <c r="B15" t="n">
-        <v>91470</v>
+        <v>91478</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405494</v>
+        <v>405561</v>
       </c>
       <c r="R15" t="n">
-        <v>6771573</v>
+        <v>6771580</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2096,7 +2096,7 @@
         <v>127862480</v>
       </c>
       <c r="B16" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127862490</v>
       </c>
       <c r="B17" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>127862470</v>
       </c>
       <c r="B18" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>127862488</v>
       </c>
       <c r="B19" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>127862474</v>
       </c>
       <c r="B20" t="n">
-        <v>98491</v>
+        <v>98505</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>127862466</v>
       </c>
       <c r="B21" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>127862506</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>127862448</v>
       </c>
       <c r="B23" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>127862494</v>
       </c>
       <c r="B24" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>127862484</v>
       </c>
       <c r="B26" t="n">
-        <v>88853</v>
+        <v>88865</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>127862442</v>
       </c>
       <c r="B27" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103659892</v>
+        <v>127862468</v>
       </c>
       <c r="B2" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fjällsåsen, Dlr</t>
+          <t>Fjällsåskölen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405566.0098262965</v>
+        <v>405599</v>
       </c>
       <c r="R2" t="n">
-        <v>6771581.277333468</v>
+        <v>6771493</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103659888</v>
+        <v>127862484</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fjällsåsen, Dlr</t>
+          <t>Fjällsåskölen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405486.504828338</v>
+        <v>405475</v>
       </c>
       <c r="R3" t="n">
-        <v>6771456.033184454</v>
+        <v>6771490</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,62 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103659889</v>
+        <v>127862482</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fjällsåsen, Dlr</t>
+          <t>Fjällsåskölen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405489.7905178164</v>
+        <v>405519</v>
       </c>
       <c r="R4" t="n">
-        <v>6771506.312973732</v>
+        <v>6771445</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,62 +954,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103659890</v>
+        <v>127862464</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fjällsåsen, Dlr</t>
+          <t>Fjällsåskölen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>405492.5896442561</v>
+        <v>405525</v>
       </c>
       <c r="R5" t="n">
-        <v>6771520.282788929</v>
+        <v>6771517</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,44 +1051,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127862450</v>
+        <v>127862508</v>
       </c>
       <c r="B6" t="n">
-        <v>92161</v>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,7 +1098,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405624</v>
+        <v>405561</v>
       </c>
       <c r="R6" t="n">
         <v>6771580</v>
@@ -1220,45 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127862464</v>
+        <v>103659892</v>
       </c>
       <c r="B7" t="n">
-        <v>91478</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fjällsåskölen, Dlr</t>
+          <t>Fjällsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405525</v>
+        <v>405566</v>
       </c>
       <c r="R7" t="n">
-        <v>6771517</v>
+        <v>6771581</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1285,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127862496</v>
+        <v>127862450</v>
       </c>
       <c r="B8" t="n">
-        <v>80152</v>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405678</v>
+        <v>405624</v>
       </c>
       <c r="R8" t="n">
-        <v>6771470</v>
+        <v>6771580</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1414,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127862510</v>
+        <v>127862454</v>
       </c>
       <c r="B9" t="n">
-        <v>92161</v>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405561</v>
+        <v>405619</v>
       </c>
       <c r="R9" t="n">
-        <v>6771580</v>
+        <v>6771567</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1511,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127862482</v>
+        <v>127862510</v>
       </c>
       <c r="B10" t="n">
-        <v>91464</v>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405519</v>
+        <v>405561</v>
       </c>
       <c r="R10" t="n">
-        <v>6771445</v>
+        <v>6771580</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1608,45 +1548,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127862452</v>
+        <v>103659889</v>
       </c>
       <c r="B11" t="n">
-        <v>91482</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fjällsåskölen, Dlr</t>
+          <t>Fjällsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405624</v>
+        <v>405490</v>
       </c>
       <c r="R11" t="n">
-        <v>6771580</v>
+        <v>6771506</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1673,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,44 +1633,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127862468</v>
+        <v>127862480</v>
       </c>
       <c r="B12" t="n">
-        <v>88865</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405599</v>
+        <v>405519</v>
       </c>
       <c r="R12" t="n">
-        <v>6771493</v>
+        <v>6771445</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1802,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127862454</v>
+        <v>127862494</v>
       </c>
       <c r="B13" t="n">
-        <v>92161</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405619</v>
+        <v>405529</v>
       </c>
       <c r="R13" t="n">
-        <v>6771567</v>
+        <v>6771570</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,45 +1839,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127862498</v>
+        <v>103659890</v>
       </c>
       <c r="B14" t="n">
-        <v>91482</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fjällsåskölen, Dlr</t>
+          <t>Fjällsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405494</v>
+        <v>405493</v>
       </c>
       <c r="R14" t="n">
-        <v>6771573</v>
+        <v>6771520</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1964,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1984,44 +1924,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127862508</v>
+        <v>127862506</v>
       </c>
       <c r="B15" t="n">
-        <v>91478</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405561</v>
+        <v>405534</v>
       </c>
       <c r="R15" t="n">
-        <v>6771580</v>
+        <v>6771422</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2093,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127862480</v>
+        <v>127862448</v>
       </c>
       <c r="B16" t="n">
-        <v>91429</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2128,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405519</v>
+        <v>405677</v>
       </c>
       <c r="R16" t="n">
-        <v>6771445</v>
+        <v>6771484</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2190,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127862490</v>
+        <v>127862470</v>
       </c>
       <c r="B17" t="n">
-        <v>80221</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2225,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405479</v>
+        <v>405608</v>
       </c>
       <c r="R17" t="n">
-        <v>6771576</v>
+        <v>6771494</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2287,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127862470</v>
+        <v>127862461</v>
       </c>
       <c r="B18" t="n">
-        <v>80192</v>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405608</v>
+        <v>405602</v>
       </c>
       <c r="R18" t="n">
-        <v>6771494</v>
+        <v>6771596</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2384,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127862488</v>
+        <v>127862490</v>
       </c>
       <c r="B19" t="n">
-        <v>91482</v>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405486</v>
+        <v>405479</v>
       </c>
       <c r="R19" t="n">
-        <v>6771515</v>
+        <v>6771576</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2481,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127862474</v>
+        <v>127862492</v>
       </c>
       <c r="B20" t="n">
-        <v>98505</v>
+        <v>5199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,19 +2432,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223597</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2512,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>405573</v>
+        <v>405529</v>
       </c>
       <c r="R20" t="n">
-        <v>6771501</v>
+        <v>6771570</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2574,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127862466</v>
+        <v>127862512</v>
       </c>
       <c r="B21" t="n">
-        <v>91482</v>
+        <v>101897</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>220075</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2609,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>405526</v>
+        <v>405561</v>
       </c>
       <c r="R21" t="n">
-        <v>6771489</v>
+        <v>6771580</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2671,45 +2615,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127862506</v>
+        <v>103659888</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>99140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fjällsåskölen, Dlr</t>
+          <t>Fjällsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>405534</v>
+        <v>405487</v>
       </c>
       <c r="R22" t="n">
-        <v>6771422</v>
+        <v>6771456</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2736,12 +2680,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2756,46 +2700,42 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127862448</v>
+        <v>127862474</v>
       </c>
       <c r="B23" t="n">
-        <v>80192</v>
+        <v>99038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>223597</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2803,10 +2743,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>405677</v>
+        <v>405573</v>
       </c>
       <c r="R23" t="n">
-        <v>6771484</v>
+        <v>6771501</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2865,10 +2805,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127862494</v>
+        <v>127862459</v>
       </c>
       <c r="B24" t="n">
-        <v>91429</v>
+        <v>80392</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2816,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2840,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>405529</v>
+        <v>405602</v>
       </c>
       <c r="R24" t="n">
-        <v>6771570</v>
+        <v>6771596</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2962,10 +2902,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127862492</v>
+        <v>127862496</v>
       </c>
       <c r="B25" t="n">
-        <v>5197</v>
+        <v>80392</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2973,21 +2913,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2937,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>405529</v>
+        <v>405678</v>
       </c>
       <c r="R25" t="n">
-        <v>6771570</v>
+        <v>6771470</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3056,200 +2996,6 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>127862484</v>
-      </c>
-      <c r="B26" t="n">
-        <v>88865</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>510</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Doftskinn</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Cystostereum murrayi</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Fjällsåskölen, Dlr</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>405475</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6771490</v>
-      </c>
-      <c r="S26" t="n">
-        <v>5</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Malung-Sälen</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Transtrand</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Olov Tranberg</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Olov Tranberg</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>127862442</v>
-      </c>
-      <c r="B27" t="n">
-        <v>91482</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Fjällsåskölen, Dlr</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>405496</v>
-      </c>
-      <c r="R27" t="n">
-        <v>6771473</v>
-      </c>
-      <c r="S27" t="n">
-        <v>5</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Malung-Sälen</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Transtrand</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Olov Tranberg</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Olov Tranberg</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20462-2025 artfynd.xlsx
+++ b/artfynd/A 20462-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862468</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862484</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862482</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862464</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862508</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103659892</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862450</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862454</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862510</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103659889</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862480</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862494</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103659890</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862506</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862448</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862470</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862461</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862490</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862492</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862512</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103659888</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2802,6 +2912,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862474</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2899,6 +3014,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862459</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2996,8 +3116,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862496</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>